--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MICHIGAN_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MICHIGAN_2023.xlsx
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C143">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C237">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C554">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C555">
